--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC2D173-D66A-4EE8-A295-F300012C2FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE16166-3A5C-491A-BDCD-F35A0FC29584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>177521.71864408237</v>
+            <v>148111.95033115722</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>274869.81610848685</v>
+            <v>319614.24010068353</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>416647.29000000004</v>
+            <v>414949.9599999999</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>177521.71864408237</v>
+        <v>148111.95033115722</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>274869.81610848685</v>
+        <v>319614.24010068353</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>416647.29000000004</v>
+        <v>414949.9599999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE16166-3A5C-491A-BDCD-F35A0FC29584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4722AA9-45B1-410D-A326-62A79E84E818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>148111.95033115722</v>
+            <v>156446.61372286209</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>319614.24010068353</v>
+            <v>307085.5970910507</v>
           </cell>
         </row>
       </sheetData>
@@ -793,11 +793,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>148111.95033115722</v>
+        <v>156446.61372286209</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>319614.24010068353</v>
+        <v>307085.5970910507</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4722AA9-45B1-410D-A326-62A79E84E818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD1F2F0-54B3-4BCA-88B2-2260C03607A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>156446.61372286209</v>
+            <v>131638.64120611723</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>307085.5970910507</v>
+            <v>352222.17704300617</v>
           </cell>
         </row>
       </sheetData>
@@ -793,11 +793,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>156446.61372286209</v>
+        <v>131638.64120611723</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>307085.5970910507</v>
+        <v>352222.17704300617</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD1F2F0-54B3-4BCA-88B2-2260C03607A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2F231F-247D-45A4-8E5E-141975B77F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>131638.64120611723</v>
+            <v>81339.133312516846</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>352222.17704300617</v>
+            <v>340324.72064911062</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>414949.9599999999</v>
+            <v>427581.07000000012</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>131638.64120611723</v>
+        <v>81339.133312516846</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>352222.17704300617</v>
+        <v>340324.72064911062</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>414949.9599999999</v>
+        <v>427581.07000000012</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2F231F-247D-45A4-8E5E-141975B77F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC96FC9-C48A-4061-9535-97C5ECE5BD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>81339.133312516846</v>
+            <v>74682.126015793518</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>340324.72064911062</v>
+            <v>340342.07687351556</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>427581.07000000012</v>
+            <v>396162.71999999986</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>81339.133312516846</v>
+        <v>74682.126015793518</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>340324.72064911062</v>
+        <v>340342.07687351556</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>427581.07000000012</v>
+        <v>396162.71999999986</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC96FC9-C48A-4061-9535-97C5ECE5BD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6D1253-DFBC-4A36-BDC5-B4A1C80B6F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>74682.126015793518</v>
+            <v>116128.90358097706</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>340342.07687351556</v>
+            <v>319879.700822627</v>
           </cell>
         </row>
       </sheetData>
@@ -793,11 +793,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>74682.126015793518</v>
+        <v>116128.90358097706</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>340342.07687351556</v>
+        <v>319879.700822627</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6D1253-DFBC-4A36-BDC5-B4A1C80B6F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101BF4A1-3D24-414D-B1A0-DEBB3A7FBC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>396162.71999999986</v>
+            <v>451749.78000000009</v>
           </cell>
         </row>
       </sheetData>
@@ -801,7 +801,7 @@
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>396162.71999999986</v>
+        <v>451749.78000000009</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101BF4A1-3D24-414D-B1A0-DEBB3A7FBC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3D212F-9F71-45DE-BD35-00407AECC4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>116128.90358097706</v>
+            <v>86478.708558612983</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>319879.700822627</v>
+            <v>304966.162957369</v>
           </cell>
         </row>
       </sheetData>
@@ -793,11 +793,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>116128.90358097706</v>
+        <v>86478.708558612983</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>319879.700822627</v>
+        <v>304966.162957369</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3D212F-9F71-45DE-BD35-00407AECC4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60D695F-7F70-4CE2-A59A-5D2DD599AF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>86478.708558612983</v>
+            <v>71317.981957891461</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>304966.162957369</v>
+            <v>290666.1570771393</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>451749.78000000009</v>
+            <v>441817.85000000009</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>86478.708558612983</v>
+        <v>71317.981957891461</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>304966.162957369</v>
+        <v>290666.1570771393</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>451749.78000000009</v>
+        <v>441817.85000000009</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60D695F-7F70-4CE2-A59A-5D2DD599AF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D0B5FA-8FF6-4A13-999C-26D7659C1851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>71317.981957891461</v>
+            <v>56923.932490944077</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>290666.1570771393</v>
+            <v>292153.47485122917</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>441817.85000000009</v>
+            <v>462026.55</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>71317.981957891461</v>
+        <v>56923.932490944077</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>290666.1570771393</v>
+        <v>292153.47485122917</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>441817.85000000009</v>
+        <v>462026.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D0B5FA-8FF6-4A13-999C-26D7659C1851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBD8CEB-9427-4E73-BA1A-9111F3AF577F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>56923.932490944077</v>
+            <v>121561.85262101516</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>292153.47485122917</v>
+            <v>276001.54440655507</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>462026.55</v>
+            <v>526491.50000000012</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>56923.932490944077</v>
+        <v>121561.85262101516</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>292153.47485122917</v>
+        <v>276001.54440655507</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>462026.55</v>
+        <v>526491.50000000012</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBD8CEB-9427-4E73-BA1A-9111F3AF577F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE4FCA1-34A7-449F-9265-2D72C24B6C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,7 +149,7 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>121561.85262101516</v>
+            <v>122213.21077101516</v>
           </cell>
         </row>
         <row r="10">
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>526491.50000000012</v>
+            <v>460498.96999999991</v>
           </cell>
         </row>
       </sheetData>
@@ -793,7 +793,7 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>121561.85262101516</v>
+        <v>122213.21077101516</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
@@ -801,7 +801,7 @@
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>526491.50000000012</v>
+        <v>460498.96999999991</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE4FCA1-34A7-449F-9265-2D72C24B6C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7D4F62-9523-495F-AB80-CC5EF1C09CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>122213.21077101516</v>
+            <v>103456.26381861775</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>276001.54440655507</v>
+            <v>287499.54992385278</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>460498.96999999991</v>
+            <v>479960.93000000017</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>122213.21077101516</v>
+        <v>103456.26381861775</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>276001.54440655507</v>
+        <v>287499.54992385278</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>460498.96999999991</v>
+        <v>479960.93000000017</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7D4F62-9523-495F-AB80-CC5EF1C09CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36EDE32-8795-4D71-B350-1DB7445C2150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>103456.26381861775</v>
+            <v>96280.685511117772</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>287499.54992385278</v>
+            <v>287083.56319918693</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>479960.93000000017</v>
+            <v>494614.25</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>103456.26381861775</v>
+        <v>96280.685511117772</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>287499.54992385278</v>
+        <v>287083.56319918693</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>479960.93000000017</v>
+        <v>494614.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36EDE32-8795-4D71-B350-1DB7445C2150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8904DE91-A182-4C0B-AAF5-7A1E2B6C3E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
   <sheets>
     <sheet name="ENERO 2026" sheetId="2" r:id="rId1"/>
@@ -22,10 +22,11 @@
     <sheet name="JULIO 2026" sheetId="8" r:id="rId7"/>
     <sheet name="AGOSTO 2026" sheetId="9" r:id="rId8"/>
     <sheet name="SEPTIEMBRE 2026" sheetId="11" r:id="rId9"/>
+    <sheet name="OCTUBRE 2026" sheetId="12" r:id="rId10"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="3">
   <si>
     <t>VALOR $ MATERIA PRIMA</t>
   </si>
@@ -128,11 +129,11 @@
       <sheetName val="MPS"/>
       <sheetName val="BOM (Recetas)"/>
       <sheetName val="Explosión de materiales"/>
-      <sheetName val="FOTORequerimienMateriaPrima09"/>
+      <sheetName val="FOTORequerimienMateriaPrima10"/>
       <sheetName val="Requerimiento Materia Prima"/>
       <sheetName val="VINCULO MP"/>
       <sheetName val="VALOR $ CONSUMO MP"/>
-      <sheetName val="FOTORequerimienMaterialConten09"/>
+      <sheetName val="FOTORequerimienMaterialConten10"/>
       <sheetName val="Requerimien Material Contenedor"/>
       <sheetName val="VINCULO MC"/>
       <sheetName val="VALOR $ CONSUMO MC"/>
@@ -149,12 +150,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>96280.685511117772</v>
+            <v>99438.311812585423</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>287083.56319918693</v>
+            <v>258536.65860655956</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +197,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>494614.25</v>
+            <v>487549.25000000006</v>
           </cell>
         </row>
       </sheetData>
@@ -530,6 +531,45 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A62089-9C49-42B8-9F67-5F0042ABFCDB}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
+        <v>99438.311812585423</v>
+      </c>
+      <c r="B2" s="1">
+        <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
+        <v>258536.65860655956</v>
+      </c>
+      <c r="C2" s="1">
+        <f>[2]Hoja1!$D$67</f>
+        <v>487549.25000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9D2DCE-DF27-47A7-94D1-74A7C977FAA7}">
   <dimension ref="A1:B2"/>
@@ -792,16 +832,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>96280.685511117772</v>
-      </c>
-      <c r="B2" s="1">
-        <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>287083.56319918693</v>
+        <v>98512</v>
+      </c>
+      <c r="B2" s="1">
+        <v>303537</v>
       </c>
       <c r="C2" s="1">
-        <f>[2]Hoja1!$D$67</f>
-        <v>494614.25</v>
+        <v>496134.86</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8904DE91-A182-4C0B-AAF5-7A1E2B6C3E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B259F76E-062B-43BB-BC29-B227FEC628BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
   <sheets>
     <sheet name="ENERO 2026" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -119,6 +119,28 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Hoja1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="67">
+          <cell r="D67">
+            <v>414082.46</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -150,12 +172,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>99438.311812585423</v>
+            <v>182726.29840555659</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>258536.65860655956</v>
+            <v>260804.22592608465</v>
           </cell>
         </row>
       </sheetData>
@@ -179,28 +201,6 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Hoja1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="67">
-          <cell r="D67">
-            <v>487549.25000000006</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -504,21 +504,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20863F6-CD25-4417-AEB7-8E59FB3D1872}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>151730.37290720001</v>
       </c>
@@ -534,13 +534,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A62089-9C49-42B8-9F67-5F0042ABFCDB}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -551,18 +551,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>99438.311812585423</v>
-      </c>
-      <c r="B2" s="1">
-        <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>258536.65860655956</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <f>'[2]DASHBOARD FINANCIERO'!$B$9</f>
+        <v>182726.29840555659</v>
+      </c>
+      <c r="B2" s="1">
+        <f>'[2]DASHBOARD FINANCIERO'!$B$10</f>
+        <v>260804.22592608465</v>
       </c>
       <c r="C2" s="1">
-        <f>[2]Hoja1!$D$67</f>
-        <v>487549.25000000006</v>
+        <f>[1]Hoja1!$D$67</f>
+        <v>414082.46</v>
       </c>
     </row>
   </sheetData>
@@ -573,21 +573,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9D2DCE-DF27-47A7-94D1-74A7C977FAA7}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>92873.219450200006</v>
       </c>
@@ -603,21 +603,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE8C23A-8E2E-4986-BEED-9671CB283657}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>227220.9444413966</v>
       </c>
@@ -633,13 +633,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AACADEB3-ADFD-433D-A188-BF7708AEE12C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -650,7 +650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>174267.59465774411</v>
       </c>
@@ -669,13 +669,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5109B6-4DFC-4F4F-89D6-D773C5A51682}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>272513.00512344769</v>
       </c>
@@ -705,13 +705,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D766F900-19C2-4C9D-9E22-92A456058EE1}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -722,7 +722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>269579.949964353</v>
       </c>
@@ -741,13 +741,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8A4453-F91D-4484-8965-25EE453231F0}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -758,7 +758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>150253.06764921913</v>
       </c>
@@ -777,13 +777,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E9A3B3-E35B-4012-8734-D5AF4CE689F0}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -794,7 +794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>154039.39212143701</v>
       </c>
@@ -813,13 +813,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD64BA53-62BA-4AC1-8141-AF32DE6DBCCD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -830,7 +830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>98512</v>
       </c>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B259F76E-062B-43BB-BC29-B227FEC628BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F41F59-C116-4478-9492-DEE9E3BCEA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
   <sheets>
     <sheet name="ENERO 2026" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
   </externalReferences>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -119,28 +119,6 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Hoja1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="67">
-          <cell r="D67">
-            <v>414082.46</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
@@ -172,12 +150,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>182726.29840555659</v>
+            <v>148747.56501353366</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>260804.22592608465</v>
+            <v>235917.84893290888</v>
           </cell>
         </row>
       </sheetData>
@@ -201,6 +179,28 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Hoja1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="67">
+          <cell r="D67">
+            <v>393793.65</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -504,21 +504,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20863F6-CD25-4417-AEB7-8E59FB3D1872}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>151730.37290720001</v>
       </c>
@@ -534,13 +534,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A62089-9C49-42B8-9F67-5F0042ABFCDB}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -551,18 +551,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <f>'[2]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>182726.29840555659</v>
-      </c>
-      <c r="B2" s="1">
-        <f>'[2]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>260804.22592608465</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
+        <v>148747.56501353366</v>
+      </c>
+      <c r="B2" s="1">
+        <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
+        <v>235917.84893290888</v>
       </c>
       <c r="C2" s="1">
-        <f>[1]Hoja1!$D$67</f>
-        <v>414082.46</v>
+        <f>[2]Hoja1!$D$67</f>
+        <v>393793.65</v>
       </c>
     </row>
   </sheetData>
@@ -573,21 +573,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9D2DCE-DF27-47A7-94D1-74A7C977FAA7}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>92873.219450200006</v>
       </c>
@@ -603,21 +603,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE8C23A-8E2E-4986-BEED-9671CB283657}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>227220.9444413966</v>
       </c>
@@ -633,13 +633,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AACADEB3-ADFD-433D-A188-BF7708AEE12C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -650,7 +650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>174267.59465774411</v>
       </c>
@@ -669,13 +669,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5109B6-4DFC-4F4F-89D6-D773C5A51682}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>272513.00512344769</v>
       </c>
@@ -705,13 +705,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D766F900-19C2-4C9D-9E22-92A456058EE1}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -722,7 +722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>269579.949964353</v>
       </c>
@@ -741,13 +741,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8A4453-F91D-4484-8965-25EE453231F0}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -758,7 +758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>150253.06764921913</v>
       </c>
@@ -777,13 +777,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E9A3B3-E35B-4012-8734-D5AF4CE689F0}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -794,7 +794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>154039.39212143701</v>
       </c>
@@ -813,13 +813,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD64BA53-62BA-4AC1-8141-AF32DE6DBCCD}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -830,7 +830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>98512</v>
       </c>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F41F59-C116-4478-9492-DEE9E3BCEA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E564B34C-63C5-4BAD-84E5-9498ACB0D5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -119,43 +119,57 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Hoja1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="67">
+          <cell r="D67">
+            <v>534411.87000000011</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
       <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="REQUERIMIENTO COMPRAS"/>
-      <sheetName val="DASHBOARD FINANCIERO"/>
-      <sheetName val="VINCULO VTS BY SKU"/>
-      <sheetName val="FILL RATE"/>
-      <sheetName val="MPS"/>
-      <sheetName val="BOM (Recetas)"/>
-      <sheetName val="Explosión de materiales"/>
-      <sheetName val="FOTORequerimienMateriaPrima10"/>
-      <sheetName val="Requerimiento Materia Prima"/>
-      <sheetName val="VINCULO MP"/>
-      <sheetName val="VALOR $ CONSUMO MP"/>
-      <sheetName val="FOTORequerimienMaterialConten10"/>
-      <sheetName val="Requerimien Material Contenedor"/>
-      <sheetName val="VINCULO MC"/>
-      <sheetName val="VALOR $ CONSUMO MC"/>
-      <sheetName val="FOTORequerimientoMaterialEmpa09"/>
-      <sheetName val="Requerimiento Material Empaque"/>
-      <sheetName val="VINCULO ME"/>
-      <sheetName val="VALOR $ CONSUMO ME"/>
-      <sheetName val="Plan Producción Semanal"/>
-      <sheetName val="Plan Maduraciòn Semanal"/>
-      <sheetName val="Panel Producción Diario"/>
+      <sheetName val="INSTRUCCIONES"/>
+      <sheetName val="EXISTENCIAS Y CIERRE"/>
+      <sheetName val="CONTEO DIARIO PRINCIPAL"/>
+      <sheetName val="CONTEO DIARIO TRÁNSITO"/>
+      <sheetName val="COMPRAS"/>
+      <sheetName val="TRASLADOS"/>
+      <sheetName val="REQUISICIONES"/>
+      <sheetName val="INICIAL"/>
+      <sheetName val="MAESTRO"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
-        <row r="9">
-          <cell r="B9">
-            <v>148747.56501353366</v>
+        <row r="4">
+          <cell r="P4">
+            <v>92510.888693558387</v>
           </cell>
         </row>
-        <row r="10">
-          <cell r="B10">
-            <v>235917.84893290888</v>
+        <row r="5">
+          <cell r="P5">
+            <v>157791.63850160004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="P6">
+            <v>121918.11961999997</v>
           </cell>
         </row>
       </sheetData>
@@ -166,41 +180,6 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Hoja1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="67">
-          <cell r="D67">
-            <v>393793.65</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -553,16 +532,16 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>148747.56501353366</v>
-      </c>
-      <c r="B2" s="1">
-        <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>235917.84893290888</v>
+        <f ca="1">'[2]EXISTENCIAS Y CIERRE'!$P$4</f>
+        <v>92510.888693558387</v>
+      </c>
+      <c r="B2" s="1">
+        <f ca="1">'[2]EXISTENCIAS Y CIERRE'!$P$5+'[2]EXISTENCIAS Y CIERRE'!$P$6</f>
+        <v>279709.75812160003</v>
       </c>
       <c r="C2" s="1">
-        <f>[2]Hoja1!$D$67</f>
-        <v>393793.65</v>
+        <f>[1]Hoja1!$D$67</f>
+        <v>534411.87000000011</v>
       </c>
     </row>
   </sheetData>
